--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_370_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_370_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1121</v>
+        <v>4.9653</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4383</v>
+        <v>3.762</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6738</v>
+        <v>1.2033</v>
       </c>
       <c r="G2" t="n">
         <v>1.9803</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9178</v>
+        <v>1.771</v>
       </c>
       <c r="T2" t="n">
-        <v>1.628</v>
+        <v>0.9517</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2898</v>
+        <v>0.8193</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5583</v>
+        <v>4.9532</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4222</v>
+        <v>3.8507</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1361</v>
+        <v>1.1025</v>
       </c>
       <c r="G3" t="n">
         <v>2.8048</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2175</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1098</v>
+        <v>0.3187</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3273</v>
+        <v>0.2937</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5037</v>
+        <v>1.6386</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3136</v>
+        <v>0.1634</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8099</v>
+        <v>1.4751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0327</v>
+        <v>-0.8389</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2283</v>
+        <v>-3.5056</v>
       </c>
       <c r="I4" t="n">
-        <v>0.261</v>
+        <v>2.6667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7298</v>
+        <v>-0.7246</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0063</v>
+        <v>-3.555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7361</v>
+        <v>2.8305</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.697</v>
+        <v>-0.1143</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.222</v>
+        <v>0.0495</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4751</v>
+        <v>-0.1638</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3292</v>
+        <v>-0.056</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9935</v>
+        <v>-0.326</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3356</v>
+        <v>0.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7501</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.254</v>
+        <v>1.4661</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0141</v>
+        <v>2.2088</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2399</v>
+        <v>-0.7427</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8389</v>
+        <v>0.0327</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.5056</v>
+        <v>-0.2283</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6667</v>
+        <v>0.261</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7246</v>
+        <v>0.7298</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.555</v>
+        <v>-0.0063</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8305</v>
+        <v>0.7361</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1143</v>
+        <v>-0.697</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0495</v>
+        <v>-0.222</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1638</v>
+        <v>-0.4751</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4406</v>
+        <v>1.2915</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4753</v>
+        <v>0.8887</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0347</v>
+        <v>0.4028</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.7501</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.553</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.05</v>
+        <v>0.068</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6029</v>
+        <v>0.7037</v>
       </c>
       <c r="G6" t="n">
         <v>0.4778</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1568</v>
+        <v>0.0619</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2773</v>
+        <v>-0.432</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3314</v>
+        <v>-1.7718</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6087</v>
+        <v>1.3398</v>
       </c>
       <c r="G7" t="n">
         <v>-3.3323</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1457</v>
+        <v>0.4364</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6176</v>
+        <v>0.1772</v>
       </c>
       <c r="U7" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V7" t="n">
         <v>1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.409</v>
+        <v>-0.9475</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1896</v>
+        <v>-2.9969</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7805</v>
+        <v>2.0494</v>
       </c>
       <c r="G8" t="n">
         <v>1.5844</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.21</v>
+        <v>0.2515</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2082</v>
+        <v>-0.0156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0018</v>
+        <v>0.2671</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4518</v>
+        <v>-1.6541</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6385</v>
+        <v>-0.8744</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8133</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5776</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0382</v>
+        <v>-0.1641</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6083</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8151</v>
+        <v>-2.3566</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4417</v>
+        <v>-3.8662</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3734</v>
+        <v>1.5096</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0554</v>
+        <v>-3.9322</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4766</v>
+        <v>-1.821</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5788</v>
+        <v>-2.1112</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7695</v>
+        <v>-2.7029</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7695</v>
+        <v>-2.1742</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2859</v>
+        <v>-1.2293</v>
       </c>
       <c r="N10" t="n">
-        <v>0.293</v>
+        <v>0.3532</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5788</v>
+        <v>-1.5825</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4722</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7196</v>
+        <v>0.2284</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2473</v>
+        <v>0.4193</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0039</v>
+        <v>-3.0681</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4127</v>
+        <v>-1.7955</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4087</v>
+        <v>-1.2726</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9322</v>
+        <v>-1.0554</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.821</v>
+        <v>-0.4766</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1112</v>
+        <v>-0.5788</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7029</v>
+        <v>-0.7695</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1742</v>
+        <v>-0.7695</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2293</v>
+        <v>-0.2859</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3532</v>
+        <v>0.293</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5825</v>
+        <v>-0.5788</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004</v>
+        <v>0.2192</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3181</v>
+        <v>0.3657</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3185</v>
+        <v>-0.1465</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7286</v>
+        <v>-4.1217</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0146</v>
+        <v>-4.3069</v>
       </c>
       <c r="F12" t="n">
-        <v>0.286</v>
+        <v>0.1852</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4989</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2324</v>
+        <v>0.3745</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5149</v>
+        <v>0.1928</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2825</v>
+        <v>0.1817</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.711</v>
+        <v>-9.3292</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.2075</v>
+        <v>-7.7921</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5035</v>
+        <v>-1.5371</v>
       </c>
       <c r="G13" t="n">
         <v>-6.2966</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5768</v>
+        <v>0.805</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2538</v>
+        <v>0.1617</v>
       </c>
       <c r="U13" t="n">
-        <v>0.677</v>
+        <v>0.6434</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7501</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.861000000000001</v>
+        <v>-8.1143</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.0978</v>
+        <v>-13.3509</v>
       </c>
       <c r="F14" t="n">
-        <v>5.236499999999999</v>
+        <v>5.2365</v>
       </c>
       <c r="G14" t="n">
         <v>-11.6519</v>
@@ -1546,13 +1546,13 @@
         <v>13.9175</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5044</v>
+        <v>6.251</v>
       </c>
       <c r="T14" t="n">
-        <v>2.126</v>
+        <v>2.8728</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3782</v>
+        <v>3.3784</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3943000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7297</v>
+        <v>3.847</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7728</v>
+        <v>3.183</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0431</v>
+        <v>0.664</v>
       </c>
       <c r="G15" t="n">
         <v>2.031</v>
@@ -1624,13 +1624,13 @@
         <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7473</v>
+        <v>-0.63</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6923</v>
+        <v>0.1026</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4396</v>
+        <v>-0.7325</v>
       </c>
       <c r="V15" t="n">
         <v>1.7501</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8051</v>
+        <v>3.2541</v>
       </c>
       <c r="E16" t="n">
         <v>0.0837</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7214</v>
+        <v>3.1704</v>
       </c>
       <c r="G16" t="n">
         <v>3.1613</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0149</v>
+        <v>0.4639</v>
       </c>
       <c r="T16" t="n">
         <v>-0.326</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3409</v>
+        <v>0.7899</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4672</v>
+        <v>2.4551</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9577</v>
+        <v>0.3642</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4249</v>
+        <v>2.0909</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4884</v>
+        <v>2.1131</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8225</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6659</v>
+        <v>2.1815</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9093</v>
+        <v>1.0303</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1814</v>
+        <v>-0.8935</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0907</v>
+        <v>1.9238</v>
       </c>
       <c r="M17" t="n">
-        <v>0.579</v>
+        <v>1.0828</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0039</v>
+        <v>0.825</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4248</v>
+        <v>0.2578</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8887</v>
+        <v>-0.7971</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4753</v>
+        <v>-0.326</v>
       </c>
       <c r="U17" t="n">
-        <v>1.364</v>
+        <v>-0.4711</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4148</v>
+        <v>2.4126</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0186</v>
+        <v>2.6096</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3963</v>
+        <v>-0.1969</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5028</v>
+        <v>2.0615</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3422</v>
+        <v>0.539</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1607</v>
+        <v>1.5224</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0878</v>
+        <v>1.3431</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1982</v>
+        <v>-0.4972</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1104</v>
+        <v>1.8402</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5906</v>
+        <v>0.7184</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5403</v>
+        <v>1.0362</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0502</v>
+        <v>-0.3178</v>
       </c>
       <c r="P18" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0158</v>
+        <v>0.1013</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3383</v>
+        <v>-0.3418</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3541</v>
+        <v>0.443</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2414</v>
+        <v>2.2182</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3642</v>
+        <v>-0.3353</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8772</v>
+        <v>2.5535</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1131</v>
+        <v>1.5028</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>1.3422</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1815</v>
+        <v>0.1607</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0303</v>
+        <v>-0.0878</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8935</v>
+        <v>-0.1982</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9238</v>
+        <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0828</v>
+        <v>1.5906</v>
       </c>
       <c r="N19" t="n">
-        <v>0.825</v>
+        <v>1.5403</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2578</v>
+        <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0108</v>
+        <v>-0.2124</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.326</v>
+        <v>-0.0156</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6849</v>
+        <v>-0.1968</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5255</v>
+        <v>1.8173</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1378</v>
+        <v>-1.1936</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6123</v>
+        <v>3.0109</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0615</v>
+        <v>1.4884</v>
       </c>
       <c r="H20" t="n">
-        <v>0.539</v>
+        <v>0.8225</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5224</v>
+        <v>0.6659</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3431</v>
+        <v>0.9093</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4972</v>
+        <v>-0.1814</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8402</v>
+        <v>1.0907</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7184</v>
+        <v>0.579</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0362</v>
+        <v>1.0039</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3178</v>
+        <v>-0.4248</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7859</v>
+        <v>0.2388</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8136</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0277</v>
+        <v>0.95</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2862</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2749</v>
+        <v>0.3713</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6135</v>
+        <v>-2.4955</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8883</v>
+        <v>2.8668</v>
       </c>
       <c r="G21" t="n">
         <v>3.2706</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1221</v>
+        <v>-0.0257</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4007</v>
+        <v>-0.2827</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2785</v>
+        <v>0.257</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0199</v>
+        <v>-0.5259</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3732</v>
+        <v>-2.1373</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3533</v>
+        <v>1.6114</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7055</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0282</v>
+        <v>-1.5343</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8136</v>
+        <v>-0.5777</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2147</v>
+        <v>-0.9566</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5407</v>
+        <v>-1.8114</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4403</v>
+        <v>-4.2044</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8996</v>
+        <v>2.393</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7702</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7705</v>
+        <v>-0.0413</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8136</v>
+        <v>-0.5777</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0431</v>
+        <v>0.5364</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0368</v>
+        <v>-2.8181</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6232</v>
+        <v>-1.5052</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4137</v>
+        <v>-1.3129</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5012</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9274</v>
+        <v>-0.7086</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4872</v>
+        <v>-0.3864</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.8612</v>
+        <v>11.2202</v>
       </c>
       <c r="E25" t="n">
         <v>-5.630800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>14.4919</v>
+        <v>16.8511</v>
       </c>
       <c r="G25" t="n">
         <v>11.6518</v>
@@ -2404,13 +2404,13 @@
         <v>16.2367</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.5044</v>
+        <v>-3.1454</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.3784</v>
+        <v>-3.3783</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.1263</v>
+        <v>0.2328999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0.3943000000000001</v>
